--- a/config/decode_values.xlsx
+++ b/config/decode_values.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\APEX LAB\Desktop\EV_Simulation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5d24e35451bcd68/Desktop/open_ev_diagnostic_tool/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD64A2D6-0652-44EF-98FB-ED405B3D53E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3D0CA6C-BDCD-49B9-84E5-93EEC89C5FD8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C3D0CA6C-BDCD-49B9-84E5-93EEC89C5FD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -592,17 +590,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A5392A-BC59-4439-8548-EE2A5DB5F062}">
   <dimension ref="A1:F24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" customWidth="1"/>
-    <col min="4" max="4" width="28.140625" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.26953125" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" customWidth="1"/>
+    <col min="3" max="3" width="24.81640625" customWidth="1"/>
+    <col min="4" max="4" width="28.1796875" customWidth="1"/>
+    <col min="5" max="5" width="30.7265625" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -642,7 +640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -662,7 +660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -682,7 +680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -702,7 +700,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -722,7 +720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -742,7 +740,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -762,7 +760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -782,7 +780,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -802,7 +800,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
@@ -822,7 +820,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
@@ -842,7 +840,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
@@ -862,7 +860,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
@@ -882,7 +880,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
@@ -902,7 +900,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
@@ -922,7 +920,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -942,7 +940,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -962,7 +960,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -982,7 +980,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="72" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="70.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -1002,7 +1000,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1022,7 +1020,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="42.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -1042,7 +1040,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
@@ -1062,7 +1060,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="28.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>49</v>
       </c>
